--- a/reports/Finance_Dashboard.xlsx
+++ b/reports/Finance_Dashboard.xlsx
@@ -14,7 +14,172 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="82">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>CONTINENTE ONLINE</t>
+  </si>
+  <si>
+    <t>debit</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>SALARIO EMPRESA XYZ</t>
+  </si>
+  <si>
+    <t>credit</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>EDP COMERCIAL</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>NETFLIX</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>WORTEN LISBOA</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>MB WAY JOAO SILVA</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>GALP COMBUSTIVEIS</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>NOS COMUNICACOES</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>PINGO DOCE</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>UBER PORTUGAL</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>FARMACIA CENTRAL</t>
+  </si>
+  <si>
+    <t>2026-04-12</t>
+  </si>
+  <si>
+    <t>SPOTIFY</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>RESTAURANTE TASCA</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>CTT EXPRESSO</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>2026-04-19</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>cafe dona</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>2026-05-03</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
   <si>
     <t>Month</t>
   </si>
@@ -31,196 +196,40 @@
     <t>Transactions</t>
   </si>
   <si>
-    <t>May 2026</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Amount</t>
+    <t>June 2026</t>
   </si>
   <si>
     <t>Category</t>
   </si>
   <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>CONTINENTE ONLINE</t>
-  </si>
-  <si>
     <t>Groceries</t>
   </si>
   <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>SALARIO EMPRESA XYZ</t>
-  </si>
-  <si>
     <t>Income</t>
   </si>
   <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>EDP COMERCIAL</t>
-  </si>
-  <si>
     <t>Utilities</t>
   </si>
   <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>NETFLIX</t>
-  </si>
-  <si>
     <t>Streaming</t>
   </si>
   <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
-    <t>WORTEN LISBOA</t>
-  </si>
-  <si>
     <t>Shopping</t>
   </si>
   <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>MB WAY JOAO SILVA</t>
-  </si>
-  <si>
     <t>Transfers</t>
   </si>
   <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>GALP COMBUSTIVEIS</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>NOS COMUNICACOES</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>PINGO DOCE</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>UBER PORTUGAL</t>
-  </si>
-  <si>
     <t>Transport</t>
   </si>
   <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>FARMACIA CENTRAL</t>
-  </si>
-  <si>
     <t>Health</t>
   </si>
   <si>
-    <t>2026-04-12</t>
-  </si>
-  <si>
-    <t>SPOTIFY</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>RESTAURANTE TASCA</t>
-  </si>
-  <si>
     <t>Food &amp; Dining</t>
   </si>
   <si>
-    <t>2026-04-14</t>
-  </si>
-  <si>
-    <t>CTT EXPRESSO</t>
-  </si>
-  <si>
     <t>Uncategorized</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-04-17</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>2026-04-19</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>2026-04-22</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>cafe dona</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
   </si>
   <si>
     <t>Amount (€)</t>
@@ -308,11 +317,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -322,16 +334,10 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -562,7 +568,499 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4">
+        <v>-45.3</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1300.0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4">
+        <v>-67.2</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4">
+        <v>-15.99</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4">
+        <v>-234.0</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4">
+        <v>50.0</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="4">
+        <v>-45.0</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4">
+        <v>-29.99</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="4">
+        <v>-38.5</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4">
+        <v>-12.3</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="4">
+        <v>-23.1</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="4">
+        <v>-9.99</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="4">
+        <v>-34.0</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="4">
+        <v>-8.5</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1300.0</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="4">
+        <v>-15.99</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="4">
+        <v>-45.3</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="4">
+        <v>-67.2</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="4">
+        <v>-45.0</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="4">
+        <v>-29.99</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="4">
+        <v>-38.5</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="4">
+        <v>-12.3</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="4">
+        <v>-23.1</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="4">
+        <v>-9.99</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="4">
+        <v>-34.0</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="4">
+        <v>-8.5</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="4">
+        <v>1300.0</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="4">
+        <v>-15.99</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="4">
+        <v>-5.0</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="4">
+        <v>-45.0</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="4">
+        <v>-29.99</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="4">
+        <v>-38.5</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="4">
+        <v>-12.3</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="4">
+        <v>-23.1</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -576,35 +1074,35 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="4">
         <v>3950.0</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>1063.62</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="4">
         <v>2886.38</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="4">
         <v>34.0</v>
       </c>
     </row>
@@ -622,493 +1120,493 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="E1" s="5"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C2" s="6">
         <v>-45.3</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
+      <c r="D2" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="C3" s="7">
         <v>1300.0</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
+      <c r="D3" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C4" s="6">
         <v>-67.2</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
+      <c r="D4" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C5" s="6">
         <v>-15.99</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
+      <c r="D5" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C6" s="6">
         <v>-234.0</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
+      <c r="D6" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>26</v>
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C7" s="7">
         <v>50.0</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
+      <c r="D7" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>29</v>
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C8" s="6">
         <v>-45.0</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
+      <c r="D8" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>31</v>
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C9" s="6">
         <v>-29.99</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
+      <c r="D9" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>33</v>
+      <c r="A10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C10" s="6">
         <v>-38.5</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>12</v>
+      <c r="D10" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>35</v>
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="C11" s="6">
         <v>-12.3</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>36</v>
+      <c r="D11" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>38</v>
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="C12" s="6">
         <v>-23.1</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>39</v>
+      <c r="D12" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>41</v>
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C13" s="6">
         <v>-9.99</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>21</v>
+      <c r="D13" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>43</v>
+      <c r="A14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C14" s="6">
         <v>-34.0</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>44</v>
+      <c r="D14" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>46</v>
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="C15" s="6">
         <v>-8.5</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>47</v>
+      <c r="D15" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>14</v>
+      <c r="A16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="C16" s="7">
         <v>1300.0</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>15</v>
+      <c r="D16" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>20</v>
+      <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C17" s="6">
         <v>-15.99</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>21</v>
+      <c r="D17" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>11</v>
+      <c r="A18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C18" s="6">
         <v>-45.3</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>12</v>
+      <c r="D18" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>17</v>
+      <c r="A19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C19" s="6">
         <v>-67.2</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>18</v>
+      <c r="D19" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>29</v>
+      <c r="A20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C20" s="6">
         <v>-45.0</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>18</v>
+      <c r="D20" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>31</v>
+      <c r="A21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C21" s="6">
         <v>-29.99</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>18</v>
+      <c r="D21" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>33</v>
+      <c r="A22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C22" s="6">
         <v>-38.5</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>12</v>
+      <c r="D22" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>35</v>
+      <c r="A23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="C23" s="6">
         <v>-12.3</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
+      <c r="D23" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>38</v>
+      <c r="A24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="C24" s="6">
         <v>-23.1</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>39</v>
+      <c r="D24" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>41</v>
+      <c r="A25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C25" s="6">
         <v>-9.99</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>21</v>
+      <c r="D25" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>43</v>
+      <c r="A26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C26" s="6">
         <v>-34.0</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>44</v>
+      <c r="D26" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>46</v>
+      <c r="A27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="C27" s="6">
         <v>-8.5</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>47</v>
+      <c r="D27" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
+      <c r="A28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="C28" s="7">
         <v>1300.0</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>15</v>
+      <c r="D28" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>20</v>
+      <c r="A29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C29" s="6">
         <v>-15.99</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>21</v>
+      <c r="D29" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>63</v>
+      <c r="A30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="C30" s="6">
         <v>-5.0</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>44</v>
+      <c r="D30" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>29</v>
+      <c r="A31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C31" s="6">
         <v>-45.0</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>18</v>
+      <c r="D31" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>31</v>
+      <c r="A32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C32" s="6">
         <v>-29.99</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>18</v>
+      <c r="D32" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>33</v>
+      <c r="A33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C33" s="6">
         <v>-38.5</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>12</v>
+      <c r="D33" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>35</v>
+      <c r="A34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="C34" s="6">
         <v>-12.3</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>36</v>
+      <c r="D34" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>38</v>
+      <c r="A35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="C35" s="6">
         <v>-23.1</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>39</v>
+      <c r="D35" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1124,102 +1622,102 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="8" t="s">
+      <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="4">
+        <v>359.37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="4">
+        <v>234.0</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="4">
+        <v>206.1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="4">
+        <v>73.0</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="3">
-        <v>359.37</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B6" s="4">
+        <v>69.3</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="4">
+        <v>67.95</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="4">
+        <v>36.9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="3">
-        <v>234.0</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="3">
-        <v>206.1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="3">
-        <v>73.0</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="3">
-        <v>69.3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="3">
-        <v>67.95</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="3">
-        <v>36.9</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>17.0</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>78</v>
+      <c r="C9" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
